--- a/artfynd/A 36968-2026 artfynd.xlsx
+++ b/artfynd/A 36968-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137416988</v>
       </c>
       <c r="B2" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137416985</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137416990</v>
       </c>
       <c r="B4" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137416981</v>
       </c>
       <c r="B5" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137416987</v>
       </c>
       <c r="B6" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>137416984</v>
       </c>
       <c r="B15" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>137416986</v>
       </c>
       <c r="B16" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>137416983</v>
       </c>
       <c r="B17" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36968-2026 artfynd.xlsx
+++ b/artfynd/A 36968-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137416988</v>
       </c>
       <c r="B2" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137416985</v>
       </c>
       <c r="B3" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137416990</v>
       </c>
       <c r="B4" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137416981</v>
       </c>
       <c r="B5" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137416987</v>
       </c>
       <c r="B6" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>137416984</v>
       </c>
       <c r="B15" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>137416986</v>
       </c>
       <c r="B16" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>137416983</v>
       </c>
       <c r="B17" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36968-2026 artfynd.xlsx
+++ b/artfynd/A 36968-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137416988</v>
       </c>
       <c r="B2" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137416985</v>
       </c>
       <c r="B3" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137416990</v>
       </c>
       <c r="B4" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137416981</v>
       </c>
       <c r="B5" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137416987</v>
       </c>
       <c r="B6" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>137416984</v>
       </c>
       <c r="B15" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>137416986</v>
       </c>
       <c r="B16" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>137416983</v>
       </c>
       <c r="B17" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36968-2026 artfynd.xlsx
+++ b/artfynd/A 36968-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137416988</v>
       </c>
       <c r="B2" t="n">
-        <v>92364</v>
+        <v>92368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137416985</v>
       </c>
       <c r="B3" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137416990</v>
       </c>
       <c r="B4" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137416981</v>
       </c>
       <c r="B5" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137416987</v>
       </c>
       <c r="B6" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137416991</v>
       </c>
       <c r="B7" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>137416992</v>
       </c>
       <c r="B8" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137416993</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>137416994</v>
       </c>
       <c r="B10" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>137416997</v>
       </c>
       <c r="B11" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>137416998</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>137416999</v>
       </c>
       <c r="B13" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>137417000</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>137416984</v>
       </c>
       <c r="B15" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>137416986</v>
       </c>
       <c r="B16" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>137416983</v>
       </c>
       <c r="B17" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
